--- a/AAII_Financials/Quarterly/FSGCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FSGCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>FSGCY</t>
   </si>
@@ -656,65 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +756,17 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,8 +797,17 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +838,17 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +861,11 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +896,17 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +937,17 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,8 +978,17 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -951,8 +1019,17 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,8 +1039,11 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -994,8 +1074,17 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1026,8 +1115,17 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1138,11 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1072,8 +1173,17 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1104,8 +1214,17 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1136,8 +1255,17 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1168,8 +1296,17 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1337,17 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,8 +1378,17 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1264,8 +1419,17 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1296,8 +1460,17 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1501,17 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1542,17 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1583,17 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,8 +1624,17 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1456,8 +1665,17 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1488,8 +1706,17 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,8 +1747,17 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1552,45 +1788,63 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1857,11 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,296 +1874,380 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>532700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>978200</v>
+      </c>
+      <c r="G41" s="3">
         <v>839900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>735500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>686800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>676800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>707600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>790100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>823000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>974600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>985500</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>264700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>184400</v>
+      </c>
+      <c r="F42" s="3">
+        <v>288500</v>
+      </c>
+      <c r="G42" s="3">
         <v>52500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>86300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
         <v>53100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
         <v>4600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="K42" s="3">
         <v>5300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="L42" s="3">
         <v>14200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <v>12800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>70600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>248500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>155000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>151100</v>
+      </c>
+      <c r="G43" s="3">
         <v>334800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>454400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>488200</v>
       </c>
-      <c r="G43" s="3">
-        <v>528400</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
+        <v>529600</v>
+      </c>
+      <c r="K43" s="3">
         <v>486400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>573800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>495100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>492400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>459600</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>225600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>232000</v>
+      </c>
+      <c r="F44" s="3">
+        <v>241000</v>
+      </c>
+      <c r="G44" s="3">
         <v>288800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>309400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>292900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>299400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>253700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>236000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>240400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>248800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>229100</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>25500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>23900</v>
+      </c>
+      <c r="G45" s="3">
         <v>33200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>43200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>40600</v>
       </c>
-      <c r="G45" s="3">
-        <v>41700</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
+        <v>40600</v>
+      </c>
+      <c r="K45" s="3">
         <v>64300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>48500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>53100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>44500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1199000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1166800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1718200</v>
+      </c>
+      <c r="G46" s="3">
         <v>1611000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>1673600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>1601000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>1585700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>1576000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>1703500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>1673500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>1872600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>1819700</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1581300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1561600</v>
+      </c>
+      <c r="F47" s="3">
+        <v>531900</v>
+      </c>
+      <c r="G47" s="3">
         <v>26700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>6200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>26800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="J47" s="3">
         <v>25800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>31200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>31500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>33600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>32500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2749100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2782900</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2875900</v>
+      </c>
+      <c r="G48" s="3">
         <v>3575300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>3644200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>3543800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>3507400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>3453000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>3216600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>3214200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>3034700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>2653900</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1076200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1093200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1130400</v>
+      </c>
+      <c r="G49" s="3">
         <v>1152400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>1192200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>1176200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>1165500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>1211200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>1158100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>1211700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>888300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>869900</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2278,17 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2319,58 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>225200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>222600</v>
+      </c>
+      <c r="G52" s="3">
         <v>317100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>340600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>307100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>288300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>281000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>272200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>277000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>273800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>245700</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2401,58 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6849100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6844700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>6493500</v>
+      </c>
+      <c r="G54" s="3">
         <v>6703600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>6878000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>6679500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>6594700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>6575500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>6403000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>6430700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>6126700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>5641500</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2465,11 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,200 +2482,257 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>258400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>186200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>285900</v>
+      </c>
+      <c r="G57" s="3">
         <v>346100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>409900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>405700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>520900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
         <v>487900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>498000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>463300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>552100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>390800</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>264200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>244700</v>
+      </c>
+      <c r="F58" s="3">
+        <v>250000</v>
+      </c>
+      <c r="G58" s="3">
         <v>371100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>418100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>365100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>368200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>328600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>391600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>515600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>507800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>428500</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>127100</v>
+      </c>
+      <c r="F59" s="3">
+        <v>120400</v>
+      </c>
+      <c r="G59" s="3">
         <v>128800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>131000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>135800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>140500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>157900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>182200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>161600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>178000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>168700</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>673900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>586100</v>
+      </c>
+      <c r="F60" s="3">
+        <v>682600</v>
+      </c>
+      <c r="G60" s="3">
         <v>914800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>1042300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>985200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>1092900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>1046200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>1189000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>1215900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>1289300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>1034000</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1407500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1528400</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1810300</v>
+      </c>
+      <c r="G61" s="3">
         <v>1975600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>1982700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>1944300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>1866800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>1782600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>1694100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>1615800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>1305600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>1164400</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>830900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>837200</v>
+      </c>
+      <c r="F62" s="3">
+        <v>90800</v>
+      </c>
+      <c r="G62" s="3">
         <v>129300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>133100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>118200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>111000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>173900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>151600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>147700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>148700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>136000</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2763,17 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2804,17 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2845,58 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2969600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3006000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2636900</v>
+      </c>
+      <c r="G66" s="3">
         <v>3101300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>3234600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>3126900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>3145600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>3086900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>3119500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>3059700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>2825500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>2406200</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2909,11 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2944,17 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,28 +2985,37 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>-578400</v>
+        <v>-488800</v>
       </c>
       <c r="E70" s="3">
-        <v>-578400</v>
+        <v>-495600</v>
       </c>
       <c r="F70" s="3">
         <v>-578400</v>
       </c>
       <c r="G70" s="3">
-        <v>-535100</v>
+        <v>-578400</v>
       </c>
       <c r="H70" s="3">
-        <v>-535100</v>
+        <v>-578400</v>
       </c>
       <c r="I70" s="3">
-        <v>-535100</v>
+        <v>-578400</v>
       </c>
       <c r="J70" s="3">
         <v>-535100</v>
@@ -2521,10 +3024,19 @@
         <v>-535100</v>
       </c>
       <c r="L70" s="3">
+        <v>-535100</v>
+      </c>
+      <c r="M70" s="3">
+        <v>-535100</v>
+      </c>
+      <c r="N70" s="3">
+        <v>-535100</v>
+      </c>
+      <c r="O70" s="3">
         <v>-535000</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +3067,58 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2520300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2500100</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2864900</v>
+      </c>
+      <c r="G72" s="3">
         <v>2733200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>2679300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>2626000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>2543700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>2526200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>2473300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>2426400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>2347600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>2320800</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +3149,17 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +3190,17 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +3231,58 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3657000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3663200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>3841700</v>
+      </c>
+      <c r="G76" s="3">
         <v>3515600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>3538200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>3451300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>3298000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>3362100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>3207800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>3257800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>3211200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>3143600</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,45 +3313,63 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2816,8 +3400,17 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3423,52 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>69700</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3">
         <v>66100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>70800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>62900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>61900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>55900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>54700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>52600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="N83" s="3">
         <v>52400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3499,17 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3540,17 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3581,17 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3622,17 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3663,58 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>87700</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3">
         <v>253200</v>
       </c>
-      <c r="E89" s="3">
-        <v>186200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>191700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>117700</v>
-      </c>
       <c r="H89" s="3">
+        <v>185700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>194000</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>116600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>252600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>205500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>204800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>103200</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3727,52 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3">
         <v>-101500</v>
       </c>
-      <c r="E91" s="3">
-        <v>-110600</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-71900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-184500</v>
-      </c>
       <c r="H91" s="3">
+        <v>-110900</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K91" s="3">
         <v>-139900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-117800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-281000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-203300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-92200</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3803,17 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3844,58 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-251500</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
         <v>-119600</v>
       </c>
-      <c r="E94" s="3">
-        <v>-144600</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-164800</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-215700</v>
-      </c>
       <c r="H94" s="3">
+        <v>-155900</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-174400</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>-61900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-234800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-672000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-131400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-167200</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,40 +3908,52 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>25900</v>
+        <v>23400</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G96" s="3">
-        <v>27600</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>25500</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>28400</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3984,17 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +4025,17 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,100 +4066,136 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-107400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-257100</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3">
         <v>-28900</v>
       </c>
-      <c r="E100" s="3">
-        <v>3900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-17400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>69900</v>
-      </c>
       <c r="H100" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>-136300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-50600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>314200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-82300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>600</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>-1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-139400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-415500</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>104400</v>
       </c>
-      <c r="E102" s="3">
-        <v>48700</v>
-      </c>
-      <c r="F102" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-30800</v>
-      </c>
       <c r="H102" s="3">
+        <v>38000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-82500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-32900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-151600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-11000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-68800</v>
       </c>
     </row>
